--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/WASHINGTON_2018.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/WASHINGTON_2018.xlsx
@@ -1363,7 +1363,7 @@
         <v>9</v>
       </c>
       <c r="D56">
-        <v>0.0009513742071881607</v>
+        <v>0.0009513742071881608</v>
       </c>
     </row>
     <row r="57">
@@ -3577,7 +3577,7 @@
         <v>9</v>
       </c>
       <c r="D179">
-        <v>0.0009513742071881607</v>
+        <v>0.0009513742071881608</v>
       </c>
     </row>
     <row r="180">
@@ -4434,7 +4434,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C227">
@@ -5305,7 +5305,7 @@
         <v>9</v>
       </c>
       <c r="D275">
-        <v>0.0009513742071881607</v>
+        <v>0.0009513742071881608</v>
       </c>
     </row>
     <row r="276">
@@ -5449,7 +5449,7 @@
         <v>9</v>
       </c>
       <c r="D283">
-        <v>0.0009513742071881607</v>
+        <v>0.0009513742071881608</v>
       </c>
     </row>
     <row r="284">
@@ -5773,7 +5773,7 @@
         <v>9</v>
       </c>
       <c r="D301">
-        <v>0.0009513742071881607</v>
+        <v>0.0009513742071881608</v>
       </c>
     </row>
     <row r="302">
@@ -5827,7 +5827,7 @@
         <v>9</v>
       </c>
       <c r="D304">
-        <v>0.0009513742071881607</v>
+        <v>0.0009513742071881608</v>
       </c>
     </row>
     <row r="305">
@@ -6007,7 +6007,7 @@
         <v>9</v>
       </c>
       <c r="D314">
-        <v>0.0009513742071881607</v>
+        <v>0.0009513742071881608</v>
       </c>
     </row>
     <row r="315">
@@ -6601,7 +6601,7 @@
         <v>9</v>
       </c>
       <c r="D347">
-        <v>0.0009513742071881607</v>
+        <v>0.0009513742071881608</v>
       </c>
     </row>
     <row r="348">
@@ -7177,7 +7177,7 @@
         <v>9</v>
       </c>
       <c r="D379">
-        <v>0.0009513742071881607</v>
+        <v>0.0009513742071881608</v>
       </c>
     </row>
     <row r="380">
@@ -7825,7 +7825,7 @@
         <v>9</v>
       </c>
       <c r="D415">
-        <v>0.0009513742071881607</v>
+        <v>0.0009513742071881608</v>
       </c>
     </row>
     <row r="416">
@@ -7843,7 +7843,7 @@
         <v>9</v>
       </c>
       <c r="D416">
-        <v>0.0009513742071881607</v>
+        <v>0.0009513742071881608</v>
       </c>
     </row>
     <row r="417">
@@ -8977,7 +8977,7 @@
         <v>92</v>
       </c>
       <c r="D479">
-        <v>0.009725158562367865</v>
+        <v>0.009725158562367863</v>
       </c>
     </row>
     <row r="480">
@@ -9841,7 +9841,7 @@
         <v>92</v>
       </c>
       <c r="D527">
-        <v>0.009725158562367865</v>
+        <v>0.009725158562367863</v>
       </c>
     </row>
     <row r="528">
@@ -9949,7 +9949,7 @@
         <v>9</v>
       </c>
       <c r="D533">
-        <v>0.0009513742071881607</v>
+        <v>0.0009513742071881608</v>
       </c>
     </row>
     <row r="534">
@@ -10381,7 +10381,7 @@
         <v>9</v>
       </c>
       <c r="D557">
-        <v>0.0009513742071881607</v>
+        <v>0.0009513742071881608</v>
       </c>
     </row>
     <row r="558">
@@ -10615,7 +10615,7 @@
         <v>9</v>
       </c>
       <c r="D570">
-        <v>0.0009513742071881607</v>
+        <v>0.0009513742071881608</v>
       </c>
     </row>
     <row r="571">
@@ -11569,7 +11569,7 @@
         <v>9</v>
       </c>
       <c r="D623">
-        <v>0.0009513742071881607</v>
+        <v>0.0009513742071881608</v>
       </c>
     </row>
     <row r="624">
@@ -13279,7 +13279,7 @@
         <v>9</v>
       </c>
       <c r="D718">
-        <v>0.0009513742071881607</v>
+        <v>0.0009513742071881608</v>
       </c>
     </row>
     <row r="719">
@@ -13452,7 +13452,7 @@
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C728">
@@ -13470,7 +13470,7 @@
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C729">
@@ -14208,7 +14208,7 @@
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C770">
@@ -14316,7 +14316,7 @@
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C776">
@@ -14359,7 +14359,7 @@
         <v>9</v>
       </c>
       <c r="D778">
-        <v>0.0009513742071881607</v>
+        <v>0.0009513742071881608</v>
       </c>
     </row>
     <row r="779">
@@ -15421,7 +15421,7 @@
         <v>9</v>
       </c>
       <c r="D837">
-        <v>0.0009513742071881607</v>
+        <v>0.0009513742071881608</v>
       </c>
     </row>
     <row r="838">
@@ -15925,7 +15925,7 @@
         <v>9</v>
       </c>
       <c r="D865">
-        <v>0.0009513742071881607</v>
+        <v>0.0009513742071881608</v>
       </c>
     </row>
     <row r="866">
@@ -16357,7 +16357,7 @@
         <v>9</v>
       </c>
       <c r="D889">
-        <v>0.0009513742071881607</v>
+        <v>0.0009513742071881608</v>
       </c>
     </row>
     <row r="890">
@@ -20533,7 +20533,7 @@
         <v>9</v>
       </c>
       <c r="D1121">
-        <v>0.0009513742071881607</v>
+        <v>0.0009513742071881608</v>
       </c>
     </row>
     <row r="1122">
@@ -20839,7 +20839,7 @@
         <v>9</v>
       </c>
       <c r="D1138">
-        <v>0.0009513742071881607</v>
+        <v>0.0009513742071881608</v>
       </c>
     </row>
     <row r="1139">
@@ -22009,7 +22009,7 @@
         <v>9</v>
       </c>
       <c r="D1203">
-        <v>0.0009513742071881607</v>
+        <v>0.0009513742071881608</v>
       </c>
     </row>
     <row r="1204">
@@ -22747,7 +22747,7 @@
         <v>9</v>
       </c>
       <c r="D1244">
-        <v>0.0009513742071881607</v>
+        <v>0.0009513742071881608</v>
       </c>
     </row>
     <row r="1245">
